--- a/public/templates/mau-nhap-topik-i-doc.xlsx
+++ b/public/templates/mau-nhap-topik-i-doc.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ĐỌC" sheetId="1" r:id="R3f1bbbe292b74f54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ĐỌC" sheetId="1" r:id="R637a2ab2037d415d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -447,7 +447,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B5" s="12" t="n">
-        <x:v>1</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -476,7 +476,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B6" s="12" t="n">
-        <x:v>2</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C6" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -505,7 +505,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B7" s="12" t="n">
-        <x:v>3</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C7" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -534,7 +534,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B8" s="12" t="n">
-        <x:v>4</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C8" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -563,7 +563,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B9" s="12" t="n">
-        <x:v>5</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C9" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -592,7 +592,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B10" s="12" t="n">
-        <x:v>6</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C10" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -621,7 +621,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B11" s="12" t="n">
-        <x:v>7</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C11" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -650,7 +650,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B12" s="12" t="n">
-        <x:v>8</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C12" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -679,7 +679,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B13" s="12" t="n">
-        <x:v>9</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C13" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -708,7 +708,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B14" s="12" t="n">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C14" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -737,7 +737,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B15" s="12" t="n">
-        <x:v>11</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C15" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -766,7 +766,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B16" s="12" t="n">
-        <x:v>12</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C16" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -795,7 +795,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B17" s="12" t="n">
-        <x:v>13</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C17" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -824,7 +824,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B18" s="12" t="n">
-        <x:v>14</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C18" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -853,7 +853,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B19" s="12" t="n">
-        <x:v>15</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C19" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -882,7 +882,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B20" s="12" t="n">
-        <x:v>16</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C20" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -911,7 +911,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B21" s="12" t="n">
-        <x:v>17</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C21" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -940,7 +940,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B22" s="12" t="n">
-        <x:v>18</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C22" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -969,7 +969,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B23" s="12" t="n">
-        <x:v>19</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C23" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -996,7 +996,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B24" s="12" t="n">
-        <x:v>20</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C24" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -1025,7 +1025,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B25" s="12" t="n">
-        <x:v>21</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C25" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -1052,7 +1052,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B26" s="12" t="n">
-        <x:v>22</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C26" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -1081,7 +1081,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B27" s="12" t="n">
-        <x:v>23</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C27" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -1108,7 +1108,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B28" s="12" t="n">
-        <x:v>24</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C28" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -1137,7 +1137,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B29" s="12" t="n">
-        <x:v>25</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C29" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -1164,7 +1164,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B30" s="12" t="n">
-        <x:v>26</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C30" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -1193,7 +1193,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B31" s="12" t="n">
-        <x:v>27</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C31" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -1220,7 +1220,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B32" s="12" t="n">
-        <x:v>28</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C32" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -1247,7 +1247,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B33" s="12" t="n">
-        <x:v>29</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C33" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -1272,7 +1272,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B34" s="12" t="n">
-        <x:v>30</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C34" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -1303,7 +1303,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B35" s="12" t="n">
-        <x:v>31</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C35" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -1330,7 +1330,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B36" s="12" t="n">
-        <x:v>32</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C36" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -1361,7 +1361,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B37" s="12" t="n">
-        <x:v>33</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C37" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -1390,7 +1390,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B38" s="12" t="n">
-        <x:v>34</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C38" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -1421,7 +1421,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B39" s="12" t="n">
-        <x:v>35</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C39" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -1448,7 +1448,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B40" s="12" t="n">
-        <x:v>36</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C40" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -1479,7 +1479,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B41" s="12" t="n">
-        <x:v>37</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C41" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -1506,7 +1506,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B42" s="12" t="n">
-        <x:v>38</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C42" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -1537,7 +1537,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B43" s="12" t="n">
-        <x:v>39</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C43" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
@@ -1564,7 +1564,7 @@
         <x:v>reading</x:v>
       </x:c>
       <x:c r="B44" s="12" t="n">
-        <x:v>40</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C44" s="14" t="str">
         <x:v>🔒 KHÓA</x:v>
